--- a/PERSONAL/1.SoftCopies/Documents Availability.xlsx
+++ b/PERSONAL/1.SoftCopies/Documents Availability.xlsx
@@ -5,28 +5,39 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Personal/1.SoftCopies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/PERSONAL/1.SoftCopies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E394E584-C1FA-49A0-A49E-0D27A49940BF}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57272E02-D689-44C9-AFB2-7896FA226658}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>DocumentCategory</t>
   </si>
@@ -143,6 +154,18 @@
   </si>
   <si>
     <t>Bank Documents</t>
+  </si>
+  <si>
+    <t>postman</t>
+  </si>
+  <si>
+    <t>Elgi@7191</t>
+  </si>
+  <si>
+    <t>New Request - My Workspace</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -217,8 +240,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -532,7 +555,7 @@
       <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -851,14 +874,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF8E5F-13D1-4AF4-A00F-7F8A4D1D7F79}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -869,29 +893,51 @@
         <v>32</v>
       </c>
       <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="https://github.com/" xr:uid="{6A32DF1D-D172-4FE7-80CB-727A1D954C1D}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://vasanth-101742-s-team.postman.co/workspace/My-Workspace~bcb24425-4a4e-4c37-8f57-6a58f5513541/http-request/39284774-9a323ce4-05fa-473b-9c0e-a3402f6fc726?sideView=agentMode" xr:uid="{FCE0252F-3A29-4469-88E6-175AF9BB4256}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
